--- a/data/trans_orig/Q4505_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q4505_R-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2007 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106809</t>
+          <t>106896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147985</t>
+          <t>146100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126446</t>
+          <t>129796</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169611</t>
+          <t>173134</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249841</t>
+          <t>250604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>309686</t>
+          <t>309601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>155481</t>
+          <t>154756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>200414</t>
+          <t>198644</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>156433</t>
+          <t>155700</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>201663</t>
+          <t>199516</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>323146</t>
+          <t>320106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>389001</t>
+          <t>384403</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>261809</t>
+          <t>264245</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>317645</t>
+          <t>316685</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>252634</t>
+          <t>253396</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>304574</t>
+          <t>304024</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>526119</t>
+          <t>530296</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>602154</t>
+          <t>602361</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35175</t>
+          <t>33679</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40149</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39531</t>
+          <t>38139</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68068</t>
+          <t>67884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60555</t>
+          <t>60741</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94972</t>
+          <t>94082</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41337</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67991</t>
+          <t>66396</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107516</t>
+          <t>109391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>150101</t>
+          <t>154335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>191436</t>
+          <t>192386</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>247473</t>
+          <t>244496</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>206937</t>
+          <t>206277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>263451</t>
+          <t>259099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>413686</t>
+          <t>415746</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>490747</t>
+          <t>491030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>198915</t>
+          <t>201186</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>249443</t>
+          <t>255459</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175263</t>
+          <t>173063</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>225988</t>
+          <t>226073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>388180</t>
+          <t>383582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>461623</t>
+          <t>463001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>366012</t>
+          <t>364358</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>426616</t>
+          <t>426651</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>379591</t>
+          <t>375570</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>438684</t>
+          <t>437315</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,47 +1690,47 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
+          <t>38,91%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>45,31%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>802111</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>757800</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>850235</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>41,63%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>39,33%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>45,45%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>802111</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>759536</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>853279</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>41,63%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>39,42%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37943</t>
+          <t>36695</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67325</t>
+          <t>66647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38369</t>
+          <t>38573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66484</t>
+          <t>67683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83125</t>
+          <t>84584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124089</t>
+          <t>124640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56217</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89474</t>
+          <t>91034</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58919</t>
+          <t>58427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92402</t>
+          <t>94318</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>126453</t>
+          <t>124781</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176840</t>
+          <t>172334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120663</t>
+          <t>119580</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>162313</t>
+          <t>162942</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151144</t>
+          <t>152002</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>195228</t>
+          <t>196398</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>282944</t>
+          <t>280149</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>347021</t>
+          <t>346618</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157211</t>
+          <t>158077</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204991</t>
+          <t>204047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158624</t>
+          <t>158020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203194</t>
+          <t>206405</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>327987</t>
+          <t>325043</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392623</t>
+          <t>390868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>246778</t>
+          <t>245899</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>298395</t>
+          <t>296543</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>212258</t>
+          <t>210438</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>260591</t>
+          <t>260640</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>478356</t>
+          <t>474042</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>548158</t>
+          <t>546354</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26528</t>
+          <t>25676</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49833</t>
+          <t>49895</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32061</t>
+          <t>32388</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56942</t>
+          <t>56334</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65685</t>
+          <t>65262</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100956</t>
+          <t>99571</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63829</t>
+          <t>64643</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35904</t>
+          <t>35852</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62622</t>
+          <t>61142</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78096</t>
+          <t>78497</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115392</t>
+          <t>116753</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>214095</t>
+          <t>213401</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>265843</t>
+          <t>266209</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>232231</t>
+          <t>233572</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>290440</t>
+          <t>289667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>461006</t>
+          <t>463471</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>541386</t>
+          <t>538100</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>216704</t>
+          <t>213668</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>268063</t>
+          <t>267133</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>222570</t>
+          <t>221047</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>279330</t>
+          <t>278339</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>451125</t>
+          <t>452945</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>528914</t>
+          <t>527230</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>303203</t>
+          <t>304830</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>363592</t>
+          <t>362449</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>351954</t>
+          <t>353832</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>416130</t>
+          <t>418261</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>673614</t>
+          <t>679184</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>758582</t>
+          <t>762508</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,52%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41727</t>
+          <t>42847</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>71352</t>
+          <t>71728</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46501</t>
+          <t>45859</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77297</t>
+          <t>76782</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>94201</t>
+          <t>97706</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>135433</t>
+          <t>141214</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61876</t>
+          <t>60177</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>94422</t>
+          <t>92890</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>64413</t>
+          <t>64671</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>101607</t>
+          <t>100984</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>136099</t>
+          <t>133864</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>184072</t>
+          <t>183087</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>676487</t>
+          <t>678719</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>776517</t>
+          <t>774598</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>765687</t>
+          <t>768582</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>867273</t>
+          <t>869708</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1476037</t>
+          <t>1476158</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1613255</t>
+          <t>1610915</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>772207</t>
+          <t>773493</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>875015</t>
+          <t>874795</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>760009</t>
+          <t>756407</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>860669</t>
+          <t>852152</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1552840</t>
+          <t>1561301</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1693811</t>
+          <t>1700355</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1234094</t>
+          <t>1231889</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1345973</t>
+          <t>1347753</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1248466</t>
+          <t>1254114</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1363501</t>
+          <t>1368033</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2516420</t>
+          <t>2521219</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2674765</t>
+          <t>2677758</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>141363</t>
+          <t>142437</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>194459</t>
+          <t>194216</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>160219</t>
+          <t>158608</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>212550</t>
+          <t>214240</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>315701</t>
+          <t>314326</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>387548</t>
+          <t>392027</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>243172</t>
+          <t>243664</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>310391</t>
+          <t>306065</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>230443</t>
+          <t>229067</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>292128</t>
+          <t>290702</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>485180</t>
+          <t>485470</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>576290</t>
+          <t>573625</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2012 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>229802</t>
+          <t>228395</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>284572</t>
+          <t>282251</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>243441</t>
+          <t>244943</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>296644</t>
+          <t>296922</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>491409</t>
+          <t>494265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>567635</t>
+          <t>565227</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>211539</t>
+          <t>214542</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>262889</t>
+          <t>266340</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>207792</t>
+          <t>208566</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259273</t>
+          <t>259025</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>438256</t>
+          <t>436272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>506982</t>
+          <t>511487</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96634</t>
+          <t>97386</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>137477</t>
+          <t>138950</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78535</t>
+          <t>78594</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>118269</t>
+          <t>117685</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>185297</t>
+          <t>185240</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>239426</t>
+          <t>240397</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26157</t>
+          <t>26058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19419</t>
+          <t>20401</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18821</t>
+          <t>17747</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39021</t>
+          <t>38657</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59497</t>
+          <t>59686</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93714</t>
+          <t>92992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65360</t>
+          <t>64653</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99990</t>
+          <t>99556</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136763</t>
+          <t>136053</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181617</t>
+          <t>183475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>369147</t>
+          <t>368587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>433518</t>
+          <t>430194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>426441</t>
+          <t>425830</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>493961</t>
+          <t>492803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>811547</t>
+          <t>812615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>902861</t>
+          <t>909707</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277494</t>
+          <t>277520</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>338179</t>
+          <t>335215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254917</t>
+          <t>253576</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312804</t>
+          <t>314964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>545909</t>
+          <t>543555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>629444</t>
+          <t>630916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140104</t>
+          <t>138647</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>188214</t>
+          <t>186157</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117511</t>
+          <t>118576</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>162551</t>
+          <t>162661</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>268528</t>
+          <t>268146</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>334005</t>
+          <t>336204</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>14684</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35226</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>23746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48416</t>
+          <t>48208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116400</t>
+          <t>114695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160329</t>
+          <t>158484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97670</t>
+          <t>99967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141767</t>
+          <t>142002</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>228567</t>
+          <t>226973</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>290641</t>
+          <t>288260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>191512</t>
+          <t>189404</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>241555</t>
+          <t>241755</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>262580</t>
+          <t>260170</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>319004</t>
+          <t>317880</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>465224</t>
+          <t>466548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>544035</t>
+          <t>542722</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>236827</t>
+          <t>235697</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>290291</t>
+          <t>288273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>194525</t>
+          <t>193128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>248887</t>
+          <t>246895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>443908</t>
+          <t>446564</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>520298</t>
+          <t>522043</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>154475</t>
+          <t>154081</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>200179</t>
+          <t>201281</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>154677</t>
+          <t>155449</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204228</t>
+          <t>204182</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>320226</t>
+          <t>322592</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>391468</t>
+          <t>392816</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34268</t>
+          <t>34993</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29313</t>
+          <t>29534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29766</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56270</t>
+          <t>55476</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64307</t>
+          <t>63727</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101974</t>
+          <t>102335</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51331</t>
+          <t>52587</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87368</t>
+          <t>85633</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125544</t>
+          <t>123997</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>174589</t>
+          <t>175087</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>284685</t>
+          <t>281515</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>345820</t>
+          <t>343319</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>376202</t>
+          <t>378421</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>440697</t>
+          <t>441761</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>679627</t>
+          <t>678669</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>771504</t>
+          <t>765291</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>290794</t>
+          <t>292124</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>350364</t>
+          <t>349646</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297820</t>
+          <t>297348</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>357363</t>
+          <t>357852</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>603973</t>
+          <t>604755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>691751</t>
+          <t>688982</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>164497</t>
+          <t>163352</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>214512</t>
+          <t>214713</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>162668</t>
+          <t>161622</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>212611</t>
+          <t>213790</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>338830</t>
+          <t>341703</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>410890</t>
+          <t>412894</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25590</t>
+          <t>25625</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51187</t>
+          <t>50414</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30079</t>
+          <t>29441</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53717</t>
+          <t>54208</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60526</t>
+          <t>61860</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96301</t>
+          <t>95031</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70045</t>
+          <t>71076</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>107938</t>
+          <t>109038</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,82 +6887,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>84482</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>66170</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>102017</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>173379</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>147623</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>198036</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>7,4%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>84482</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>66065</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>102184</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>173379</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>150057</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>203061</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1123637</t>
+          <t>1129058</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1240803</t>
+          <t>1242078</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1373165</t>
+          <t>1367563</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1494471</t>
+          <t>1488382</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2532836</t>
+          <t>2525657</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2699555</t>
+          <t>2697519</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1067129</t>
+          <t>1072054</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1184702</t>
+          <t>1185338</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1009027</t>
+          <t>1009721</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1130887</t>
+          <t>1117834</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2113731</t>
+          <t>2113990</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2276395</t>
+          <t>2266264</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>595712</t>
+          <t>597110</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>686404</t>
+          <t>685257</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>559919</t>
+          <t>557659</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>652356</t>
+          <t>647796</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1176670</t>
+          <t>1172052</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1309295</t>
+          <t>1308391</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>69131</t>
+          <t>69718</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>107927</t>
+          <t>107753</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>74816</t>
+          <t>74416</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>115500</t>
+          <t>113486</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>156375</t>
+          <t>152195</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>210570</t>
+          <t>207349</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>343099</t>
+          <t>342315</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>421818</t>
+          <t>421223</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>318361</t>
+          <t>319911</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>390712</t>
+          <t>393594</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>685701</t>
+          <t>686385</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>793920</t>
+          <t>794657</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>180381</t>
+          <t>180720</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>232298</t>
+          <t>231085</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>187650</t>
+          <t>190063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234181</t>
+          <t>235792</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>381723</t>
+          <t>379923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>451166</t>
+          <t>454766</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>187229</t>
+          <t>190102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>235651</t>
+          <t>239931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202150</t>
+          <t>201817</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248849</t>
+          <t>251879</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>405522</t>
+          <t>404249</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>471604</t>
+          <t>469372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>126569</t>
+          <t>130158</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>173130</t>
+          <t>173765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113166</t>
+          <t>112804</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>154726</t>
+          <t>155588</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256573</t>
+          <t>254526</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>316040</t>
+          <t>313759</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>25592</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25426</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>22589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44480</t>
+          <t>45030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75104</t>
+          <t>75672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111539</t>
+          <t>112560</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65947</t>
+          <t>67523</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100445</t>
+          <t>102228</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149743</t>
+          <t>151274</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>203138</t>
+          <t>201655</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>312222</t>
+          <t>313010</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>377494</t>
+          <t>376687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>331665</t>
+          <t>334475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>396192</t>
+          <t>396010</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>655621</t>
+          <t>661928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>746694</t>
+          <t>746177</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>335718</t>
+          <t>334940</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>399997</t>
+          <t>400372</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318068</t>
+          <t>318326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>379561</t>
+          <t>378816</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>670502</t>
+          <t>673291</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>755432</t>
+          <t>761966</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>163099</t>
+          <t>162571</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>213473</t>
+          <t>215103</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>195428</t>
+          <t>195487</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>249005</t>
+          <t>247044</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>376054</t>
+          <t>377110</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>448813</t>
+          <t>447980</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41316</t>
+          <t>41621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,82 +9052,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>22668</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14748</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>34108</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>52078</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>39108</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>68853</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>22668</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14496</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>33364</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>52078</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>38797</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>68483</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72955</t>
+          <t>73149</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109872</t>
+          <t>111097</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71604</t>
+          <t>70574</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108148</t>
+          <t>108677</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153309</t>
+          <t>151806</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>205907</t>
+          <t>204951</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>194120</t>
+          <t>191964</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>243042</t>
+          <t>245047</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>208673</t>
+          <t>212320</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>259482</t>
+          <t>262657</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>418642</t>
+          <t>413014</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>490205</t>
+          <t>487252</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>297708</t>
+          <t>297029</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>353165</t>
+          <t>354882</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>340191</t>
+          <t>339551</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>396825</t>
+          <t>394358</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>657148</t>
+          <t>659080</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>737897</t>
+          <t>741288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,36%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>133158</t>
+          <t>133389</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>179833</t>
+          <t>180550</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>118217</t>
+          <t>117803</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>163157</t>
+          <t>163413</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>264401</t>
+          <t>264759</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>326278</t>
+          <t>328048</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>12056</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29555</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>17168</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>19806</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41106</t>
+          <t>41726</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23406</t>
+          <t>23398</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46532</t>
+          <t>48341</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19159</t>
+          <t>19606</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41184</t>
+          <t>42586</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48934</t>
+          <t>48896</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81227</t>
+          <t>79480</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>330584</t>
+          <t>332215</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>391204</t>
+          <t>390129</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>375950</t>
+          <t>378238</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>440912</t>
+          <t>442697</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>727523</t>
+          <t>723014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>812993</t>
+          <t>812307</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,04%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>287276</t>
+          <t>289570</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>344988</t>
+          <t>347099</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>316100</t>
+          <t>316714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>379166</t>
+          <t>378790</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>624915</t>
+          <t>622665</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>708544</t>
+          <t>705722</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>125934</t>
+          <t>125720</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>168940</t>
+          <t>169358</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>136107</t>
+          <t>137886</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>186149</t>
+          <t>186065</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>275849</t>
+          <t>278277</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>338793</t>
+          <t>339095</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19168</t>
+          <t>18592</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39382</t>
+          <t>39870</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15538</t>
+          <t>15142</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36140</t>
+          <t>34989</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>39444</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67967</t>
+          <t>69705</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68949</t>
+          <t>68480</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>105180</t>
+          <t>102710</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>82308</t>
+          <t>82116</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123574</t>
+          <t>122103</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>158952</t>
+          <t>159475</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>213198</t>
+          <t>213814</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1066588</t>
+          <t>1068962</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1183060</t>
+          <t>1181252</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,82 +10759,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>34,95%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1215028</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1155477</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>1274286</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>34,37%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>32,68%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>36,04%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>2188</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2339420</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2257395</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>2420267</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>33,83%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>32,64%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>35,0%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1215028</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1156941</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>1273370</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>34,37%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>32,72%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>36,02%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>2188</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>2339420</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>2260512</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>2416707</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>33,83%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>32,69%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1159440</t>
+          <t>1167784</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1277849</t>
+          <t>1278505</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1224702</t>
+          <t>1230410</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1345994</t>
+          <t>1351481</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2427982</t>
+          <t>2423545</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2592379</t>
+          <t>2591063</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>599759</t>
+          <t>592625</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>692457</t>
+          <t>691476</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>613951</t>
+          <t>610757</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>709785</t>
+          <t>700730</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1225222</t>
+          <t>1230195</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1364484</t>
+          <t>1367556</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>75290</t>
+          <t>74759</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>114159</t>
+          <t>114775</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>56832</t>
+          <t>58597</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>89661</t>
+          <t>92002</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>142149</t>
+          <t>141123</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>193030</t>
+          <t>193470</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>268277</t>
+          <t>269586</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>338408</t>
+          <t>335878</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>268760</t>
+          <t>269945</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>335269</t>
+          <t>335473</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>559674</t>
+          <t>554127</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>653048</t>
+          <t>654712</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4505_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q4505_R-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106896</t>
+          <t>108682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146100</t>
+          <t>150911</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129796</t>
+          <t>131072</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>173134</t>
+          <t>168575</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>250604</t>
+          <t>249241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>309601</t>
+          <t>309176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>154756</t>
+          <t>155140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>198644</t>
+          <t>199729</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155700</t>
+          <t>155464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199516</t>
+          <t>199596</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>320106</t>
+          <t>320201</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>384403</t>
+          <t>384941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>264245</t>
+          <t>261173</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>316685</t>
+          <t>316020</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>253396</t>
+          <t>252751</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>304024</t>
+          <t>304062</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>530296</t>
+          <t>528472</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>602361</t>
+          <t>600178</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>33458</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19370</t>
+          <t>18999</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39757</t>
+          <t>40398</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38139</t>
+          <t>39082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67884</t>
+          <t>67777</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60741</t>
+          <t>59550</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94082</t>
+          <t>94542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39937</t>
+          <t>40643</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66396</t>
+          <t>67971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109391</t>
+          <t>110235</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154335</t>
+          <t>151894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>192386</t>
+          <t>191140</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>244496</t>
+          <t>245991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>206277</t>
+          <t>207334</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>259099</t>
+          <t>259450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>415746</t>
+          <t>414394</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>491030</t>
+          <t>494320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>201186</t>
+          <t>202675</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>255459</t>
+          <t>258090</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173063</t>
+          <t>174794</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>226073</t>
+          <t>222624</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>383582</t>
+          <t>384131</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>463001</t>
+          <t>462409</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>364358</t>
+          <t>363771</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>426651</t>
+          <t>430311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>375570</t>
+          <t>377785</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>437315</t>
+          <t>439861</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>757800</t>
+          <t>759021</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>850235</t>
+          <t>853023</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36695</t>
+          <t>39019</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66647</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38573</t>
+          <t>38876</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67683</t>
+          <t>67459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84584</t>
+          <t>83356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124640</t>
+          <t>126208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>55547</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91034</t>
+          <t>90497</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58427</t>
+          <t>59759</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94318</t>
+          <t>93726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124781</t>
+          <t>123513</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172334</t>
+          <t>171872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119580</t>
+          <t>117777</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>162942</t>
+          <t>163029</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152002</t>
+          <t>149865</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>196398</t>
+          <t>197847</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>280149</t>
+          <t>283647</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>346618</t>
+          <t>344637</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158077</t>
+          <t>154898</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204047</t>
+          <t>203633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158020</t>
+          <t>158621</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206405</t>
+          <t>205195</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>325043</t>
+          <t>328312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>390868</t>
+          <t>393725</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>245899</t>
+          <t>247470</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>296543</t>
+          <t>299986</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>210438</t>
+          <t>213588</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>260640</t>
+          <t>266210</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>474042</t>
+          <t>478382</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>546354</t>
+          <t>546527</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,17%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>25047</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49895</t>
+          <t>48585</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32388</t>
+          <t>32085</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56334</t>
+          <t>57922</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,47 +2485,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>79567</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>64497</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>99934</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>4,74%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>79567</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>65262</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>99571</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36710</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64643</t>
+          <t>63351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35852</t>
+          <t>34703</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61142</t>
+          <t>60709</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78497</t>
+          <t>77454</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>116753</t>
+          <t>116251</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>213401</t>
+          <t>215552</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>266209</t>
+          <t>267554</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>233572</t>
+          <t>233325</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>289667</t>
+          <t>291406</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>463471</t>
+          <t>462598</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>538100</t>
+          <t>540348</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>213668</t>
+          <t>212284</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>267133</t>
+          <t>265929</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>221047</t>
+          <t>222339</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>278339</t>
+          <t>277404</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>452945</t>
+          <t>453207</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>527230</t>
+          <t>526568</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>304830</t>
+          <t>300856</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>362449</t>
+          <t>360026</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>353832</t>
+          <t>355132</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>418261</t>
+          <t>415239</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>679184</t>
+          <t>674255</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>762508</t>
+          <t>757112</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42847</t>
+          <t>42848</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>71728</t>
+          <t>72716</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45859</t>
+          <t>46852</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76782</t>
+          <t>78340</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>97706</t>
+          <t>96735</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>141214</t>
+          <t>139345</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60177</t>
+          <t>60792</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>92890</t>
+          <t>93756</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>64671</t>
+          <t>64782</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>100984</t>
+          <t>101893</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>133864</t>
+          <t>134153</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>183087</t>
+          <t>181820</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>678719</t>
+          <t>674257</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>774598</t>
+          <t>774223</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>768582</t>
+          <t>767333</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>869708</t>
+          <t>865963</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1476158</t>
+          <t>1478653</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1610915</t>
+          <t>1616955</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>773493</t>
+          <t>765846</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>874795</t>
+          <t>868116</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>756407</t>
+          <t>754215</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>852152</t>
+          <t>857804</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1561301</t>
+          <t>1551499</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1700355</t>
+          <t>1695007</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1231889</t>
+          <t>1229065</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1347753</t>
+          <t>1347323</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1254114</t>
+          <t>1253063</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1368033</t>
+          <t>1364092</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2521219</t>
+          <t>2512973</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2677758</t>
+          <t>2668079</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>142437</t>
+          <t>141577</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>194216</t>
+          <t>193967</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>158608</t>
+          <t>159913</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>214240</t>
+          <t>213679</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>314326</t>
+          <t>317075</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>392027</t>
+          <t>386925</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>243664</t>
+          <t>243391</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>306065</t>
+          <t>306416</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>229067</t>
+          <t>227236</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>290702</t>
+          <t>286242</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>485470</t>
+          <t>488364</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>573625</t>
+          <t>575222</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>228395</t>
+          <t>229798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>282251</t>
+          <t>284098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>244943</t>
+          <t>245138</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>296922</t>
+          <t>300064</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>494265</t>
+          <t>488801</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>565227</t>
+          <t>563162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214542</t>
+          <t>214476</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266340</t>
+          <t>265581</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>208566</t>
+          <t>209893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259025</t>
+          <t>260160</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>436272</t>
+          <t>435172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>511487</t>
+          <t>510938</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97386</t>
+          <t>96136</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138950</t>
+          <t>136408</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78594</t>
+          <t>78272</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117685</t>
+          <t>118114</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>185240</t>
+          <t>184972</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>240397</t>
+          <t>243735</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26058</t>
+          <t>25796</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20401</t>
+          <t>20211</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17747</t>
+          <t>18117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>41108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59686</t>
+          <t>60293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92992</t>
+          <t>93991</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64653</t>
+          <t>65958</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99556</t>
+          <t>99443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136053</t>
+          <t>134200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183475</t>
+          <t>184429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>368587</t>
+          <t>366015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>430194</t>
+          <t>431356</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>425830</t>
+          <t>427159</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>492803</t>
+          <t>492235</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>812615</t>
+          <t>815475</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>909707</t>
+          <t>905220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277520</t>
+          <t>275064</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>335215</t>
+          <t>335917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>253576</t>
+          <t>251775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>314964</t>
+          <t>311242</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543555</t>
+          <t>547188</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>630916</t>
+          <t>631579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>138647</t>
+          <t>139199</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>186157</t>
+          <t>186200</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118576</t>
+          <t>116277</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>162661</t>
+          <t>163650</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>268146</t>
+          <t>268069</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>336204</t>
+          <t>332567</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19461</t>
+          <t>20340</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35680</t>
+          <t>35090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23746</t>
+          <t>23889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48208</t>
+          <t>48447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114695</t>
+          <t>114962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158484</t>
+          <t>159186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99967</t>
+          <t>98584</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142002</t>
+          <t>143228</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>226973</t>
+          <t>225891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>288260</t>
+          <t>286669</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>189404</t>
+          <t>188943</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>241755</t>
+          <t>241623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>260170</t>
+          <t>264351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>317880</t>
+          <t>321626</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>466548</t>
+          <t>463188</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>542722</t>
+          <t>542221</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>235697</t>
+          <t>236009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>288273</t>
+          <t>292267</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193128</t>
+          <t>195877</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>246895</t>
+          <t>245915</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>446564</t>
+          <t>445587</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>522043</t>
+          <t>522584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>154081</t>
+          <t>151864</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>201281</t>
+          <t>202710</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>155449</t>
+          <t>154385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204182</t>
+          <t>202693</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>322592</t>
+          <t>318931</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>392816</t>
+          <t>387830</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34993</t>
+          <t>34973</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29534</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29766</t>
+          <t>27898</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55476</t>
+          <t>56332</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63727</t>
+          <t>62582</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102335</t>
+          <t>101302</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52587</t>
+          <t>51425</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85633</t>
+          <t>84324</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123997</t>
+          <t>125839</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>175087</t>
+          <t>177688</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>281515</t>
+          <t>282810</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>343319</t>
+          <t>343686</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>378421</t>
+          <t>375674</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>441761</t>
+          <t>439244</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>678669</t>
+          <t>679434</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>765291</t>
+          <t>763538</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>292124</t>
+          <t>290807</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>349646</t>
+          <t>349387</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297348</t>
+          <t>297908</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>357852</t>
+          <t>358221</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>604755</t>
+          <t>603191</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>688982</t>
+          <t>689800</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>163352</t>
+          <t>163807</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>214713</t>
+          <t>212651</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>161622</t>
+          <t>161397</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>213790</t>
+          <t>213385</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>341703</t>
+          <t>339735</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>412894</t>
+          <t>412527</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25625</t>
+          <t>26554</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50414</t>
+          <t>51180</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>28651</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54208</t>
+          <t>54300</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61860</t>
+          <t>62126</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95031</t>
+          <t>96623</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71076</t>
+          <t>71950</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>109038</t>
+          <t>110891</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,82 +6887,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>84482</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>68285</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>103285</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>173379</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>149643</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>202187</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>7,51%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>11,52%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>84482</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>66170</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>102017</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>6,32%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>173379</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>147623</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>198036</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1129058</t>
+          <t>1128880</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1242078</t>
+          <t>1244784</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1367563</t>
+          <t>1376265</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1488382</t>
+          <t>1488485</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2525657</t>
+          <t>2537282</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2697519</t>
+          <t>2702436</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1072054</t>
+          <t>1071245</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1185338</t>
+          <t>1184473</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1009721</t>
+          <t>1006070</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1117834</t>
+          <t>1114018</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2113990</t>
+          <t>2105545</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2266264</t>
+          <t>2268808</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>597110</t>
+          <t>594989</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>685257</t>
+          <t>691368</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>557659</t>
+          <t>560625</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>647796</t>
+          <t>650223</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1172052</t>
+          <t>1176155</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1308391</t>
+          <t>1305896</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>69718</t>
+          <t>69271</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>107753</t>
+          <t>108913</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>74416</t>
+          <t>75250</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>113486</t>
+          <t>115363</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>152195</t>
+          <t>159259</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>207349</t>
+          <t>209859</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>342315</t>
+          <t>346173</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>421223</t>
+          <t>424718</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>319911</t>
+          <t>316041</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>393594</t>
+          <t>389948</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>686385</t>
+          <t>681361</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>794657</t>
+          <t>789989</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>180720</t>
+          <t>182774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>231085</t>
+          <t>231245</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190063</t>
+          <t>187484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>235792</t>
+          <t>238604</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>379923</t>
+          <t>380202</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>454766</t>
+          <t>447976</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>190102</t>
+          <t>188306</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239931</t>
+          <t>236354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>201817</t>
+          <t>200079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251879</t>
+          <t>249257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>404249</t>
+          <t>402237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>469372</t>
+          <t>474188</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,24%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130158</t>
+          <t>130151</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>173765</t>
+          <t>174733</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>112804</t>
+          <t>114322</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155588</t>
+          <t>155584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>254526</t>
+          <t>252938</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>313759</t>
+          <t>314096</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25592</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22589</t>
+          <t>22307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45030</t>
+          <t>44272</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75672</t>
+          <t>73800</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>112560</t>
+          <t>111368</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67523</t>
+          <t>68046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102228</t>
+          <t>101306</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151274</t>
+          <t>152126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201655</t>
+          <t>201231</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>313010</t>
+          <t>312162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>376687</t>
+          <t>375599</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>334475</t>
+          <t>332018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>396010</t>
+          <t>393519</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>661928</t>
+          <t>658500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>746177</t>
+          <t>746093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>334940</t>
+          <t>332894</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>400372</t>
+          <t>399146</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318326</t>
+          <t>317216</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>378816</t>
+          <t>381149</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>673291</t>
+          <t>673399</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>761966</t>
+          <t>759797</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>162571</t>
+          <t>164190</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215103</t>
+          <t>214706</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>195487</t>
+          <t>196486</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>247044</t>
+          <t>249190</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>377110</t>
+          <t>373191</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>447980</t>
+          <t>444979</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>19411</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41621</t>
+          <t>42108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34108</t>
+          <t>35017</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39108</t>
+          <t>39349</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68853</t>
+          <t>69589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73149</t>
+          <t>71858</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111097</t>
+          <t>109127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70574</t>
+          <t>71198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108677</t>
+          <t>109433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151806</t>
+          <t>153466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>204951</t>
+          <t>206024</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>191964</t>
+          <t>190970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>245047</t>
+          <t>243320</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>212320</t>
+          <t>210887</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>262657</t>
+          <t>263721</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>413014</t>
+          <t>416922</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>487252</t>
+          <t>491124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>297029</t>
+          <t>297182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>354882</t>
+          <t>355203</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>339551</t>
+          <t>339279</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>394358</t>
+          <t>393480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>659080</t>
+          <t>653550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>741288</t>
+          <t>733416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,85%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>133389</t>
+          <t>133313</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180550</t>
+          <t>179761</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>117803</t>
+          <t>119935</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>163413</t>
+          <t>162008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>264759</t>
+          <t>263157</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>328048</t>
+          <t>327600</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30570</t>
+          <t>29630</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17168</t>
+          <t>16624</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19806</t>
+          <t>20339</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41726</t>
+          <t>41548</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23398</t>
+          <t>23497</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48341</t>
+          <t>47047</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19606</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42586</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48896</t>
+          <t>48634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79480</t>
+          <t>81150</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>332215</t>
+          <t>327299</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>390129</t>
+          <t>387273</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>378238</t>
+          <t>372733</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>442697</t>
+          <t>440100</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>723014</t>
+          <t>724172</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>812307</t>
+          <t>810991</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>289570</t>
+          <t>288919</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>347099</t>
+          <t>345155</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>316714</t>
+          <t>317149</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>378790</t>
+          <t>381564</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>622665</t>
+          <t>627362</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>705722</t>
+          <t>709451</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>125720</t>
+          <t>126701</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>169358</t>
+          <t>170098</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>137886</t>
+          <t>138492</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>186065</t>
+          <t>187469</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278277</t>
+          <t>276636</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>339095</t>
+          <t>338688</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39870</t>
+          <t>39390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15142</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34989</t>
+          <t>35583</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39444</t>
+          <t>39981</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69705</t>
+          <t>67393</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68480</t>
+          <t>68077</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>102710</t>
+          <t>104264</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>82116</t>
+          <t>82985</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>122103</t>
+          <t>121752</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>159475</t>
+          <t>161037</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>213814</t>
+          <t>214507</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1068962</t>
+          <t>1068733</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1181252</t>
+          <t>1184644</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1155477</t>
+          <t>1161183</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1274286</t>
+          <t>1272512</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2257395</t>
+          <t>2257105</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2420267</t>
+          <t>2418791</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1167784</t>
+          <t>1166569</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1278505</t>
+          <t>1277738</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1230410</t>
+          <t>1237339</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1351481</t>
+          <t>1348309</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2423545</t>
+          <t>2434277</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2591063</t>
+          <t>2587854</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>592625</t>
+          <t>598127</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>691476</t>
+          <t>687573</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>610757</t>
+          <t>610735</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>700730</t>
+          <t>701099</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1230195</t>
+          <t>1233914</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1367556</t>
+          <t>1361323</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>74759</t>
+          <t>75437</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>114775</t>
+          <t>112199</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>58597</t>
+          <t>56998</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>92002</t>
+          <t>90734</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>141123</t>
+          <t>142282</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>193470</t>
+          <t>193745</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>269586</t>
+          <t>268845</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>335878</t>
+          <t>339359</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>269945</t>
+          <t>268458</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>335473</t>
+          <t>339782</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>554127</t>
+          <t>557717</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>654712</t>
+          <t>652247</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
